--- a/artfynd/A 2657-2024 artfynd.xlsx
+++ b/artfynd/A 2657-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2657-2024 artfynd.xlsx
+++ b/artfynd/A 2657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,6 +1583,458 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115017927</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 2657, Möckelhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573749</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6387554</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115017949</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 2657, Möckelhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573778</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6387529</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115017742</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 2657, Möckelhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573524</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6387405</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115017732</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 2657, Möckelhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573505</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6387378</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2657-2024 artfynd.xlsx
+++ b/artfynd/A 2657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>66246440</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573489.0362306903</v>
+        <v>573489</v>
       </c>
       <c r="R2" t="n">
-        <v>6387430.409106821</v>
+        <v>6387430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114420060</v>
+        <v>114417904</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,21 +821,16 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573609</v>
+        <v>573670</v>
       </c>
       <c r="R3" t="n">
-        <v>6387379</v>
+        <v>6387440</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -875,19 +860,9 @@
           <t>2024-01-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-01-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,19 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114417904</v>
+        <v>114420060</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,16 +919,21 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573670</v>
+        <v>573609</v>
       </c>
       <c r="R4" t="n">
-        <v>6387440</v>
+        <v>6387379</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -988,9 +963,19 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114417987</v>
+        <v>114420194</v>
       </c>
       <c r="B5" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,38 +1013,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573627</v>
+        <v>573615</v>
       </c>
       <c r="R5" t="n">
-        <v>6387433</v>
+        <v>6387375</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,61 +1115,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114418530</v>
+        <v>114424309</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573691</v>
+        <v>573573</v>
       </c>
       <c r="R6" t="n">
-        <v>6387507</v>
+        <v>6387436</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,28 +1184,17 @@
           <t>2024-01-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-01-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1251,59 +1213,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114420194</v>
+        <v>114418530</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573615</v>
+        <v>573691</v>
       </c>
       <c r="R7" t="n">
-        <v>6387375</v>
+        <v>6387507</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1301,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,6 +1310,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1369,54 +1329,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114424309</v>
+        <v>115017732</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>A 2657, Möckelhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573573</v>
+        <v>573505</v>
       </c>
       <c r="R8" t="n">
-        <v>6387436</v>
+        <v>6387378</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,72 +1420,79 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114418102</v>
+        <v>115017742</v>
       </c>
       <c r="B9" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norra Sandvik (Norra Sandvik), Sm</t>
+          <t>A 2657, Möckelhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573644</v>
+        <v>573524</v>
       </c>
       <c r="R9" t="n">
-        <v>6387488</v>
+        <v>6387405</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,22 +1516,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,18 +1530,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1588,12 +1552,7 @@
         <v>115017927</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,12 +1658,7 @@
         <v>115017949</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,65 +1761,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115017742</v>
+        <v>114417987</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 2657, Möckelhult, Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573524</v>
+        <v>573627</v>
       </c>
       <c r="R12" t="n">
-        <v>6387405</v>
+        <v>6387433</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,12 +1827,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,84 +1851,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115017732</v>
+        <v>114418102</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2657, Möckelhult, Sm</t>
+          <t>Norra Sandvik, Norra Sandvik, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573505</v>
+        <v>573644</v>
       </c>
       <c r="R13" t="n">
-        <v>6387378</v>
+        <v>6387488</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,12 +1935,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,22 +1959,127 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115017769</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 2657, Möckelhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>573548</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6387374</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
